--- a/pipeline/credit_rating/output/xhtn_tong_hop_20261003.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20261003.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2111,7 +2111,7 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2233,7 +2233,7 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2655,7 +2655,7 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2739,7 +2739,7 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -3991,7 +3991,7 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4079,7 +4079,7 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4649,7 +4649,7 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -4875,7 +4875,7 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14747,7 +14747,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16379,7 +16379,7 @@
       <c r="AD140" t="inlineStr"/>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17533,7 +17533,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18447,7 +18447,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18681,7 +18681,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19359,7 +19359,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -20031,7 +20031,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21101,7 +21101,7 @@
       <c r="AD181" t="inlineStr"/>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21229,7 +21229,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21345,7 +21345,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21841,7 +21841,7 @@
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -22053,7 +22053,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23309,7 +23309,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23877,7 +23877,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -23989,7 +23989,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24117,7 +24117,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24469,7 +24469,7 @@
       <c r="AD210" t="inlineStr"/>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24595,7 +24595,7 @@
       <c r="AD211" t="inlineStr"/>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24721,7 +24721,7 @@
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -25065,7 +25065,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25639,7 +25639,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25865,7 +25865,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25993,7 +25993,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -26105,7 +26105,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26445,7 +26445,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26667,7 +26667,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26777,7 +26777,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26897,7 +26897,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -27013,7 +27013,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27129,7 +27129,7 @@
       </c>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27257,7 +27257,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27819,7 +27819,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -28049,7 +28049,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28169,7 +28169,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28503,7 +28503,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28837,7 +28837,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28949,7 +28949,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29179,7 +29179,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29291,7 +29291,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29401,7 +29401,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29649,7 +29649,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29759,7 +29759,7 @@
       </c>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29869,7 +29869,7 @@
       </c>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29979,7 +29979,7 @@
       </c>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30091,7 +30091,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30201,7 +30201,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30545,7 +30545,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30657,7 +30657,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30773,7 +30773,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30889,7 +30889,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -30999,7 +30999,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31225,7 +31225,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31341,7 +31341,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31683,7 +31683,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31793,7 +31793,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -32013,7 +32013,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32113,7 +32113,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32335,7 +32335,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32445,7 +32445,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32677,7 +32677,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33015,7 +33015,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33127,7 +33127,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33353,7 +33353,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33463,7 +33463,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33589,7 +33589,7 @@
       <c r="AD290" t="inlineStr"/>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33717,7 +33717,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33829,7 +33829,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33929,7 +33929,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34029,7 +34029,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34143,7 +34143,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34257,7 +34257,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34357,7 +34357,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34477,7 +34477,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34589,7 +34589,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34701,7 +34701,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34815,7 +34815,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34929,7 +34929,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35175,7 +35175,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35303,7 +35303,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35431,7 +35431,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35559,7 +35559,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35671,7 +35671,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35783,7 +35783,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35893,7 +35893,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36131,7 +36131,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36241,7 +36241,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36481,7 +36481,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36593,7 +36593,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36703,7 +36703,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36823,7 +36823,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -37071,7 +37071,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37307,7 +37307,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37423,7 +37423,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37535,7 +37535,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37663,7 +37663,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37791,7 +37791,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -38015,7 +38015,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38351,7 +38351,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38463,7 +38463,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38583,7 +38583,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38711,7 +38711,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38827,7 +38827,7 @@
       </c>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38927,7 +38927,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39167,7 +39167,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39291,7 +39291,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39513,7 +39513,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39623,7 +39623,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39733,7 +39733,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39843,7 +39843,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -40073,7 +40073,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40183,7 +40183,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40293,7 +40293,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40533,7 +40533,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40653,7 +40653,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40773,7 +40773,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40889,7 +40889,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -41005,7 +41005,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -41121,7 +41121,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41233,7 +41233,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41349,7 +41349,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41469,7 +41469,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41581,7 +41581,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41697,7 +41697,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41813,7 +41813,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41929,7 +41929,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -42045,7 +42045,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:03</t>
+          <t>2026-10-03 13:38:15</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42275,7 +42275,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42391,7 +42391,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42507,7 +42507,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42617,7 +42617,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42845,7 +42845,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42955,7 +42955,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -43067,7 +43067,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43179,7 +43179,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43411,7 +43411,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43539,7 +43539,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43659,7 +43659,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43899,7 +43899,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -44009,7 +44009,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44119,7 +44119,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44343,7 +44343,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44453,7 +44453,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44569,7 +44569,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44679,7 +44679,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44791,7 +44791,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44901,7 +44901,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -45011,7 +45011,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45139,7 +45139,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45251,7 +45251,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45379,7 +45379,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45491,7 +45491,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45601,7 +45601,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45821,7 +45821,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45933,7 +45933,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -46043,7 +46043,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46171,7 +46171,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46283,7 +46283,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46393,7 +46393,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46503,7 +46503,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46613,7 +46613,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46723,7 +46723,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46833,7 +46833,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46945,7 +46945,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47073,7 +47073,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47183,7 +47183,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47293,7 +47293,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47405,7 +47405,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47627,7 +47627,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47865,7 +47865,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47977,7 +47977,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48087,7 +48087,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48197,7 +48197,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48307,7 +48307,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48407,7 +48407,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48517,7 +48517,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48617,7 +48617,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48727,7 +48727,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48855,7 +48855,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49075,7 +49075,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49185,7 +49185,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49295,7 +49295,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49405,7 +49405,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49515,7 +49515,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49625,7 +49625,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49735,7 +49735,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49863,7 +49863,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50075,7 +50075,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50185,7 +50185,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50299,7 +50299,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50409,7 +50409,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50509,7 +50509,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50621,7 +50621,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50843,7 +50843,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -50955,7 +50955,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51067,7 +51067,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51177,7 +51177,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51305,7 +51305,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51437,7 +51437,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51569,7 +51569,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51701,7 +51701,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51825,7 +51825,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51937,7 +51937,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52037,7 +52037,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52157,7 +52157,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52273,7 +52273,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52385,7 +52385,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52507,7 +52507,7 @@
       <c r="AD455" t="inlineStr"/>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52619,7 +52619,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52729,7 +52729,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52839,7 +52839,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52949,7 +52949,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -53059,7 +53059,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53187,7 +53187,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53303,7 +53303,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53413,7 +53413,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53541,7 +53541,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53669,7 +53669,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53797,7 +53797,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53925,7 +53925,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -54037,7 +54037,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54147,7 +54147,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54275,7 +54275,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54387,7 +54387,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54499,7 +54499,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54615,7 +54615,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54727,7 +54727,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54839,7 +54839,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54951,7 +54951,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -55063,7 +55063,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55183,7 +55183,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55293,7 +55293,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55421,7 +55421,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55541,7 +55541,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55653,7 +55653,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55765,7 +55765,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55865,7 +55865,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55981,7 +55981,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -56091,7 +56091,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56203,7 +56203,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56313,7 +56313,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56425,7 +56425,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56537,7 +56537,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56637,7 +56637,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56747,7 +56747,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56859,7 +56859,7 @@
       </c>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56969,7 +56969,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -57079,7 +57079,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57191,7 +57191,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57301,7 +57301,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57411,7 +57411,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57521,7 +57521,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57641,7 +57641,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57765,7 +57765,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:05</t>
+          <t>2026-10-03 13:38:17</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57875,7 +57875,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57987,7 +57987,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58097,7 +58097,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58209,7 +58209,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58321,7 +58321,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58431,7 +58431,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58541,7 +58541,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58651,7 +58651,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58761,7 +58761,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58871,7 +58871,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58981,7 +58981,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59205,7 +59205,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59317,7 +59317,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59427,7 +59427,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59539,7 +59539,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59639,7 +59639,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59749,7 +59749,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59849,7 +59849,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -59949,7 +59949,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60061,7 +60061,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60173,7 +60173,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60285,7 +60285,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60395,7 +60395,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60505,7 +60505,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60615,7 +60615,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60727,7 +60727,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60837,7 +60837,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -60947,7 +60947,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61057,7 +61057,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61167,7 +61167,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61279,7 +61279,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61391,7 +61391,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61507,7 +61507,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61635,7 +61635,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61747,7 +61747,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61857,7 +61857,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -61977,7 +61977,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62087,7 +62087,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62197,7 +62197,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62307,7 +62307,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62427,7 +62427,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62543,7 +62543,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62655,7 +62655,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62775,7 +62775,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62887,7 +62887,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -62987,7 +62987,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63107,7 +63107,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63217,7 +63217,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63329,7 +63329,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63445,7 +63445,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63557,7 +63557,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63669,7 +63669,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63797,7 +63797,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63907,7 +63907,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64017,7 +64017,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64127,7 +64127,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64239,7 +64239,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64367,7 +64367,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64479,7 +64479,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64591,7 +64591,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64703,7 +64703,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64803,7 +64803,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64913,7 +64913,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -65023,7 +65023,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65123,7 +65123,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65233,7 +65233,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65361,7 +65361,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65471,7 +65471,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65583,7 +65583,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65693,7 +65693,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65805,7 +65805,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65915,7 +65915,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66025,7 +66025,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66125,7 +66125,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66235,7 +66235,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66347,7 +66347,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66457,7 +66457,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66567,7 +66567,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66677,7 +66677,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66787,7 +66787,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66897,7 +66897,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67007,7 +67007,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67107,7 +67107,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67217,7 +67217,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67327,7 +67327,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67439,7 +67439,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67549,7 +67549,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67661,7 +67661,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67771,7 +67771,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67881,7 +67881,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -67991,7 +67991,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68101,7 +68101,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68211,7 +68211,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68323,7 +68323,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68433,7 +68433,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68545,7 +68545,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68657,7 +68657,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68767,7 +68767,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68879,7 +68879,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -68991,7 +68991,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69101,7 +69101,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69211,7 +69211,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69321,7 +69321,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69431,7 +69431,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69531,7 +69531,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69643,7 +69643,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69753,7 +69753,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69863,7 +69863,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -69991,7 +69991,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70103,7 +70103,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70215,7 +70215,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70343,7 +70343,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70455,7 +70455,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70583,7 +70583,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70711,7 +70711,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70823,7 +70823,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70935,7 +70935,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71045,7 +71045,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71157,7 +71157,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71267,7 +71267,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71377,7 +71377,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71489,7 +71489,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71601,7 +71601,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71713,7 +71713,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71823,7 +71823,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71933,7 +71933,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72045,7 +72045,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72157,7 +72157,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72267,7 +72267,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72379,7 +72379,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72489,7 +72489,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72589,7 +72589,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72699,7 +72699,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72811,7 +72811,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72921,7 +72921,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73033,7 +73033,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73143,7 +73143,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73253,7 +73253,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73363,7 +73363,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73473,7 +73473,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73583,7 +73583,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73695,7 +73695,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73805,7 +73805,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73915,7 +73915,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74025,7 +74025,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74137,7 +74137,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74247,7 +74247,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74359,7 +74359,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74471,7 +74471,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74571,7 +74571,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74681,7 +74681,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74793,7 +74793,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74905,7 +74905,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75017,7 +75017,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75129,7 +75129,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75239,7 +75239,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75349,7 +75349,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75461,7 +75461,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75571,7 +75571,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75683,7 +75683,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75783,7 +75783,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75893,7 +75893,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -76005,7 +76005,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76115,7 +76115,7 @@
       <c r="AD666" t="inlineStr"/>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-10-03 09:24:19</t>
+          <t>2026-10-03 13:38:32</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76227,7 +76227,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76339,7 +76339,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76449,7 +76449,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76561,7 +76561,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76661,7 +76661,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76761,7 +76761,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76861,7 +76861,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -76973,7 +76973,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77073,7 +77073,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77183,7 +77183,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77283,7 +77283,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77395,7 +77395,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77507,7 +77507,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77619,7 +77619,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77731,7 +77731,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77831,7 +77831,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -77943,7 +77943,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78053,7 +78053,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78165,7 +78165,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78265,7 +78265,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78365,7 +78365,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78465,7 +78465,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78565,7 +78565,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78677,7 +78677,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78789,7 +78789,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -78889,7 +78889,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -78999,7 +78999,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79111,7 +79111,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79223,7 +79223,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79335,7 +79335,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79447,7 +79447,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79559,7 +79559,7 @@
       </c>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79671,7 +79671,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79783,7 +79783,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -79883,7 +79883,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -79983,7 +79983,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80095,7 +80095,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:48</t>
+          <t>2026-10-03 13:38:00</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80195,7 +80195,7 @@
       </c>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80295,7 +80295,7 @@
       </c>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80395,7 +80395,7 @@
       </c>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80505,7 +80505,7 @@
       </c>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80605,7 +80605,7 @@
       </c>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
@@ -80715,7 +80715,7 @@
       </c>
       <c r="AE709" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF709" t="inlineStr">
@@ -80797,7 +80797,7 @@
       <c r="AD710" t="inlineStr"/>
       <c r="AE710" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF710" t="inlineStr">
@@ -80879,7 +80879,7 @@
       <c r="AD711" t="inlineStr"/>
       <c r="AE711" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF711" t="inlineStr">
@@ -80961,7 +80961,7 @@
       <c r="AD712" t="inlineStr"/>
       <c r="AE712" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF712" t="inlineStr">
@@ -81043,7 +81043,7 @@
       <c r="AD713" t="inlineStr"/>
       <c r="AE713" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:58</t>
+          <t>2026-10-03 13:38:08</t>
         </is>
       </c>
       <c r="AF713" t="inlineStr">
